--- a/Замены.xlsx
+++ b/Замены.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ремонт Демо-ГРП-1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ремонт ШРП МР-1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ремонт ГРП №2 (блочный)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №1 — ГРП 2006 г" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №2 — ГРП 2012 г" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №3 — ГРП 2012 г" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №4 — ГРП 2016 г" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №5 — ГРП 2001 г" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,15 +29,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -56,14 +69,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -442,54 +458,192 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Дата замены запасной части</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Номер запчасти</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Модель оборудования</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Производитель оборудования</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Тип объекта (ГРП, ШРП)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Номер объекта</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Вид работ при замене запасной части</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Причина замены (замена по графику или описание неисправности)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11.2011</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>КРОН-50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2006 г.: подходит срок полной проверки (20 лет)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Замена мембраны и уплотнений регулятора (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Петров П.П.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11.2016</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>КРОН-50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2006 г.: подходит срок полной проверки (20 лет)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>61</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Замена клапана регулятора и мембраны (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Петров П.П.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11.2021</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>КРОН-50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2006 г.: подходит срок полной проверки (20 лет)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>61</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Замена мембраны, колец, клапана (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Петров П.П.</t>
         </is>
       </c>
     </row>
@@ -504,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -520,54 +674,146 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Дата замены запасной части</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Номер запчасти</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Модель оборудования</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Производитель оборудования</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Тип объекта (ГРП, ШРП)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Номер объекта</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Вид работ при замене запасной части</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Причина замены (замена по графику или описание неисправности)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>08.2018</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>РГП-50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №2 — ГРП 2012 г.: в 2018 г. оборудование вышло из строя</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Аварийная замена</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Отказ регулятора: разрыв мембраны, срабатывание ПЗК</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Сидоров С.С.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>08.2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>РГП-50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №2 — ГРП 2012 г.: в 2018 г. оборудование вышло из строя</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Замена мембраны и уплотнительных колец (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Сидоров С.С.</t>
         </is>
       </c>
     </row>
@@ -582,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -598,54 +844,624 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Дата замены запасной части</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Номер запчасти</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Модель оборудования</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Производитель оборудования</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Тип объекта (ГРП, ШРП)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Номер объекта</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Вид работ при замене запасной части</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Причина замены (замена по графику или описание неисправности)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>03.2017</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>КРОН-150</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2012 г.: полная замена оборудования каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>63</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Аварийная замена</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Отказ оборудования: разрыв мембраны, потеря герметичности</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Кузнецов К.К.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>05.2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>КРОН-150</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2012 г.: полная замена оборудования каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>63</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Аварийная замена</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Разрушение клапана регулятора, аварийный сброс</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Кузнецов К.К.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>05.2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ПСК-50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2012 г.: полная замена оборудования каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>63</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Аварийная замена</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Отказ предохранительного клапана</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Кузнецов К.К.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Дата замены запасной части</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Номер запчасти</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Модель оборудования</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Производитель оборудования</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Тип объекта (ГРП, ШРП)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Номер объекта</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Вид работ при замене запасной части</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Причина замены (замена по графику или описание неисправности)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>09.2021</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>РДГПК-50М</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №4 — ГРП 2016 г.: оборудование не менялось, ресурс в норме</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>64</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Замена мембраны и уплотнительных колец (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09.2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>РДГПК-50М</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №4 — ГРП 2016 г.: оборудование не менялось, ресурс в норме</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>64</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Замена мембраны, колец, фильтрующего элемента (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Дата замены запасной части</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Номер запчасти</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Модель оборудования</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Производитель оборудования</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Тип объекта (ГРП, ШРП)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Номер объекта</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Вид работ при замене запасной части</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Причина замены (замена по графику или описание неисправности)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>06.2009</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>РДК-50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Замена мембраны</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09.2014</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ПКН(В)-100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Повреждение седла клапана, износ уплотнений</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11.2019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ПСК-50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Течь по уплотнению, негерметичность</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12.2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>РДК-50</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>65</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Износ клапана, деформация мембраны</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
         </is>
       </c>
     </row>

--- a/Замены.xlsx
+++ b/Замены.xlsx
@@ -6,11 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №1 — ГРП 2006 г" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №2 — ГРП 2012 г" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №3 — ГРП 2012 г" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №4 — ГРП 2016 г" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №5 — ГРП 2001 г" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №2 — ГРП 2012 г" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №3 — ГРП 2008 г" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №1 — ГРП 2008 г" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -442,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -512,7 +510,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11.2011</t>
+          <t>09.2013</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -523,7 +521,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>КРОН-50</t>
+          <t>РГП-50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,32 +531,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2006 г.: подходит срок полной проверки (20 лет)</t>
+          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Замена мембраны и уплотнений регулятора (срок 5 лет)</t>
+          <t>Замена 3 деталей: мембрана, седло, прокладка</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Петров П.П.</t>
+          <t>Волков В.В.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11.2016</t>
+          <t>03.2014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -569,7 +567,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>КРОН-50</t>
+          <t>РГП-50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -579,32 +577,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2006 г.: подходит срок полной проверки (20 лет)</t>
+          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Замена клапана регулятора и мембраны (срок 5 лет)</t>
+          <t>Замена 3 деталей: втулка, тарелка, кольцо</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Петров П.П.</t>
+          <t>Волков В.В.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11.2021</t>
+          <t>09.2015</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -615,7 +613,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>КРОН-50</t>
+          <t>РГП-50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,25 +623,117 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2006 г.: подходит срок полной проверки (20 лет)</t>
+          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Замена мембраны, колец, клапана (срок 5 лет)</t>
+          <t>Замена 2 деталей: шток, гайка</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Петров П.П.</t>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>03.2016</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ПКН(В)-100А</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>103</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Замена 3 деталей: пружина, втулка, кольцо</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09.2017</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ПСК-50</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>103</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Замена 2 деталей: клапан, винт</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
         </is>
       </c>
     </row>
@@ -653,562 +743,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Дата замены запасной части</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Номер запчасти</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Модель оборудования</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Производитель оборудования</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Тип объекта (ГРП, ШРП)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Номер объекта</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Вид работ при замене запасной части</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Причина замены (замена по графику или описание неисправности)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>ФИО руководителя газоопасных работ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>08.2018</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Регулятор</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>РГП-50</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Сценарий №2 — ГРП 2012 г.: в 2018 г. оборудование вышло из строя</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>62</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Аварийная замена</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Отказ регулятора: разрыв мембраны, срабатывание ПЗК</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Сидоров С.С.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>08.2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Регулятор</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>РГП-50</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Сценарий №2 — ГРП 2012 г.: в 2018 г. оборудование вышло из строя</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>62</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Плановый ремонт</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Замена мембраны и уплотнительных колец (срок 5 лет)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Сидоров С.С.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Дата замены запасной части</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Номер запчасти</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Модель оборудования</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Производитель оборудования</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Тип объекта (ГРП, ШРП)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Номер объекта</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Вид работ при замене запасной части</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Причина замены (замена по графику или описание неисправности)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>ФИО руководителя газоопасных работ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>03.2017</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Регулятор</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>КРОН-150</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Сценарий №3 — ГРП 2012 г.: полная замена оборудования каждые 5 лет</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>63</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Аварийная замена</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Отказ оборудования: разрыв мембраны, потеря герметичности</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Кузнецов К.К.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>05.2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Регулятор</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>КРОН-150</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Сценарий №3 — ГРП 2012 г.: полная замена оборудования каждые 5 лет</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>63</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Аварийная замена</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Разрушение клапана регулятора, аварийный сброс</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Кузнецов К.К.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>05.2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Клапан</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ПСК-50</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Сценарий №3 — ГРП 2012 г.: полная замена оборудования каждые 5 лет</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>63</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Аварийная замена</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Отказ предохранительного клапана</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Кузнецов К.К.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Дата замены запасной части</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Номер запчасти</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Модель оборудования</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Производитель оборудования</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Тип объекта (ГРП, ШРП)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Номер объекта</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Вид работ при замене запасной части</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Причина замены (замена по графику или описание неисправности)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>ФИО руководителя газоопасных работ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>09.2021</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Регулятор</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>РДГПК-50М</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Сценарий №4 — ГРП 2016 г.: оборудование не менялось, ресурс в норме</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>64</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Плановый ремонт</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Замена мембраны и уплотнительных колец (срок 5 лет)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Морозов М.М.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>09.2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Регулятор</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>РДГПК-50М</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Сценарий №4 — ГРП 2016 г.: оборудование не менялось, ресурс в норме</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>64</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Плановый ремонт</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Замена мембраны, колец, фильтрующего элемента (срок 5 лет)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Морозов М.М.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1284,7 +818,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06.2009</t>
+          <t>05.2013</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -1295,21 +829,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>РДК-50</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1318,7 +852,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Замена мембраны</t>
+          <t>Замена 3 деталей: седло, пружина, прокладка</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1330,32 +864,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09.2014</t>
+          <t>05.2018</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Регулятор</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ПКН(В)-100</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1364,7 +898,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Повреждение седла клапана, износ уплотнений</t>
+          <t>Замена 3 деталей: седло, пружина, прокладка</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1376,41 +910,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11.2019</t>
+          <t>05.2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Регулятор</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ПСК-50</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Текущий ремонт</t>
+          <t>Плановый ремонт</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Течь по уплотнению, негерметичность</t>
+          <t>Замена 3 деталей: седло, пружина, прокладка</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1422,7 +956,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12.2023</t>
+          <t>03.2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1433,35 +967,343 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>РДК-50</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>ООО «Газпроммаш»</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>104</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Замена мембраны — расходной детали, срок менее года</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Дата замены запасной части</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Номер запчасти</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Модель оборудования</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Производитель оборудования</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Тип объекта (ГРП, ШРП)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Номер объекта</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Вид работ при замене запасной части</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Причина замены (замена по графику или описание неисправности)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>04.2013</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>РДГПК-100</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>АО «Газмаш»</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>107</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Замена мембраны, пружины, седла, колец (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>04.2018</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>РДГПК-100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>107</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Замена мембраны, пружины, седла, колец (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>04.2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>РДГПК-100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>107</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Замена мембраны, пружины, седла, колец (срок 5 лет)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04.2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ПКН(В)-100А</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Сценарий №5 — ГРП 2001 г.: срок истёк, замен не проводилось</t>
+          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Текущий ремонт</t>
+          <t>Плановый ремонт</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Износ клапана, деформация мембраны</t>
+          <t>Замена пружины, втулки, колец</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Волков В.В.</t>
+          <t>Морозов М.М.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>04.2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ПСК-50</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>АО «Газмаш»</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>107</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Замена клапана, винта, колец</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
         </is>
       </c>
     </row>

--- a/Замены.xlsx
+++ b/Замены.xlsx
@@ -6,9 +6,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №2 — ГРП 2012 г" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №3 — ГРП 2008 г" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №1 — ГРП 2008 г" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №1 — ГРП 2008 г" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №2 — ГРП 2012 г" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №3 — ГРП 2016 г" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №4 — ГРП 2021 г" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -510,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09.2013</t>
+          <t>05.2013</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -521,30 +522,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>РГП-50</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
+          <t>Сценарий №1 — ГРП 2008 г.: часть запчастей с истёкшим сроком</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Текущий ремонт</t>
+          <t>Плановый ремонт</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Замена 3 деталей: мембрана, седло, прокладка</t>
+          <t>Замена 3 деталей: седло, пружина, прокладка</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -556,7 +557,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03.2014</t>
+          <t>05.2018</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -567,30 +568,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>РГП-50</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
+          <t>Сценарий №1 — ГРП 2008 г.: часть запчастей с истёкшим сроком</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Текущий ремонт</t>
+          <t>Плановый ремонт</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Замена 3 деталей: втулка, тарелка, кольцо</t>
+          <t>Замена 3 деталей: седло, пружина, прокладка</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -602,7 +603,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09.2015</t>
+          <t>05.2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -613,30 +614,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>РГП-50</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
+          <t>Сценарий №1 — ГРП 2008 г.: часть запчастей с истёкшим сроком</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Текущий ремонт</t>
+          <t>Плановый ремонт</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Замена 2 деталей: шток, гайка</t>
+          <t>Замена 3 деталей: седло, пружина, прокладка</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -648,32 +649,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03.2016</t>
+          <t>03.2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Регулятор</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ПКН(В)-100А</t>
+          <t>КРОН-150</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
+          <t>Сценарий №1 — ГРП 2008 г.: часть запчастей с истёкшим сроком</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -682,58 +683,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Замена 3 деталей: пружина, втулка, кольцо</t>
+          <t>Замена мембраны — расходной детали, срок менее года</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Морозов М.М.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09.2017</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Клапан</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ПСК-50</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Сценарий №2 — ГРП 2012 г.: по 2-3 разные запчасти раз в полгода</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>103</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Текущий ремонт</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Замена 2 деталей: клапан, винт</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Морозов М.М.</t>
+          <t>Волков В.В.</t>
         </is>
       </c>
     </row>
@@ -818,7 +773,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05.2013</t>
+          <t>12.2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -829,30 +784,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>КРОН-150</t>
+          <t>РГП-50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ООО «Газпроммаш»</t>
+          <t>АО «Газмаш»</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
+          <t>Сценарий №2 — ГРП 2012 г.: ресурс запчастей менее года</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Замена 3 деталей: седло, пружина, прокладка</t>
+          <t>Замена мембраны — расходная деталь, меняется чаще остальных</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -864,99 +819,99 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05.2018</t>
+          <t>06.2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Регулятор</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>КРОН-150</t>
+          <t>ПКН(В)-100А</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ООО «Газпроммаш»</t>
+          <t>АО «Газмаш»</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
+          <t>Сценарий №2 — ГРП 2012 г.: ресурс запчастей менее года</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Замена 3 деталей: седло, пружина, прокладка</t>
+          <t>Замена пружины и втулки</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Волков В.В.</t>
+          <t>Морозов М.М.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05.2023</t>
+          <t>03.2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Регулятор</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>КРОН-150</t>
+          <t>ПСК-50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ООО «Газпроммаш»</t>
+          <t>АО «Газмаш»</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
+          <t>Сценарий №2 — ГРП 2012 г.: ресурс запчастей менее года</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Замена 3 деталей: седло, пружина, прокладка</t>
+          <t>Замена клапана и винта</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Волков В.В.</t>
+          <t>Морозов М.М.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03.2026</t>
+          <t>09.2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -967,21 +922,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>КРОН-150</t>
+          <t>РГП-50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ООО «Газпроммаш»</t>
+          <t>АО «Газмаш»</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Сценарий №3 — ГРП 2008 г.: 2-3 запчасти планово, одна — каждые полгода</t>
+          <t>Сценарий №2 — ГРП 2012 г.: ресурс запчастей менее года</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -990,7 +945,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Замена мембраны — расходной детали, срок менее года</t>
+          <t>Замена седла и прокладки</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1005,6 +960,268 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Дата замены запасной части</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Номер запчасти</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Модель оборудования</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Производитель оборудования</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Тип объекта (ГРП, ШРП)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Номер объекта</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Вид работ при замене запасной части</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Причина замены (замена по графику или описание неисправности)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>06.2021</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>РДК-50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ООО «Газпроммаш»</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2016 г.: ресурс запчастей в норме</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>137</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Плановый ремонт</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Замена мембраны, седла, прокладки</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11.2022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>КРОН-50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ООО «Газпроммаш»</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2016 г.: ресурс запчастей в норме</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>137</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Замена пружины и втулки</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02.2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ПЗКП-32</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ООО «Газпроммаш»</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2016 г.: ресурс запчастей в норме</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>137</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Замена клапана, винта, колец</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Морозов М.М.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>08.2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Регулятор</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>РГП-32</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ООО «Газпроммаш»</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Сценарий №3 — ГРП 2016 г.: ресурс запчастей в норме</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>137</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Текущий ремонт</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Замена мембраны и прокладки</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Волков В.В.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1080,10 +1297,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04.2013</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>10.2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>11-93.32.00.010Б-01</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Регулятор</t>
@@ -1091,42 +1312,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>РДГПК-100</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>АО «Газмаш»</t>
+          <t>Регулятор давления газа РДС-32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+          <t>Сценарий №4 — ГРП 2021 г.: замены запчастей недавние</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>При ТР</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Замена мембраны, пружины, седла, колец (срок 5 лет)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Волков В.В.</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04.2018</t>
+          <t>10.2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -1137,30 +1353,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>РДГПК-100</t>
+          <t>КРОН-200</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+          <t>Сценарий №4 — ГРП 2021 г.: замены запчастей недавние</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Замена мембраны, пружины, седла, колец (срок 5 лет)</t>
+          <t>Замена мембраны после пусконаладки</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1172,7 +1388,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04.2023</t>
+          <t>04.2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -1183,30 +1399,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>РДГПК-100</t>
+          <t>РГК-100</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+          <t>Сценарий №4 — ГРП 2021 г.: замены запчастей недавние</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Замена мембраны, пружины, седла, колец (срок 5 лет)</t>
+          <t>Замена седла и прокладки</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1218,7 +1434,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04.2023</t>
+          <t>11.2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1229,30 +1445,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ПКН(В)-100А</t>
+          <t>ПСК-50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+          <t>Сценарий №4 — ГРП 2021 г.: замены запчастей недавние</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Замена пружины, втулки, колец</t>
+          <t>Замена клапана и пружины</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1264,41 +1480,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04.2023</t>
+          <t>07.2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Регулятор</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ПСК-50</t>
+          <t>РДГПК-50М</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>АО «Газмаш»</t>
+          <t>ООО «Газпроммаш»</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Сценарий №1 — ГРП 2008 г.: плановые замены запчастей каждые 5 лет</t>
+          <t>Сценарий №4 — ГРП 2021 г.: замены запчастей недавние</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Плановый ремонт</t>
+          <t>Текущий ремонт</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Замена клапана, винта, колец</t>
+          <t>Замена мембраны и фильтра</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/Замены.xlsx
+++ b/Замены.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №2 — ГРП 2012 г" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №3 — ГРП 2016 г" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт Сценарий №4 — ГРП 2021 г" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ремонт ГРП №26" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1526,4 +1527,410 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Дата замены запасной части</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Номер запчасти</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тип оборудования (Регулятор, ПСК, ПЗК, Фильтр)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Модель оборудования</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Производитель оборудования</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Тип объекта (ГРП, ШРП)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Номер объекта</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Вид работ при замене запасной части</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Причина замены (замена по графику или описание неисправности)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФИО руководителя газоопасных работ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>03.2024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный запорный ПКН-50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ПКН-50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Белгазтехника</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>157</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Проверка параметров срабатывания, настройка оборудования</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Плановое ТО</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>05.2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Фильтр газовый ФГМ-50</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ФГМ-50</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Белгазтехника</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>157</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Техническое обслуживание, очистка</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Плановое ТО</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11.2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Фильтр газовый ФГМ-50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ФГМ-50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Белгазтехника</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>157</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ТО с испытанием приборного оборудования</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Плановое ТО</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>05.2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Газовое оборудование, ПТК «Region-gaz»</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>157</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ТО с испытанием приборного оборудования</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Плановое ТО</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11.2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Газовое оборудование, ПТК «Region-gaz»</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>157</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ТО с испытанием приборного оборудования, настройка</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Плановое ТО</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05.2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Регулятор давления газа РДБК-1М-50/35</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>РДБК-1М-50/35</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Белгазтехника</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>157</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Разборка, очистка, притирка седла и клапана, повторная настройка</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Нарушение герметичности затвора при нулевом расходе (Pвых = 2,93 кПа, превышение допуска)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05.2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Газовое оборудование, ПТК «Region-gaz»</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>157</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ТО, повторное диагностирование после ремонта</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>05.2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Газовое оборудование, ПТК «Region-gaz»</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ГРП №26</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>157</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Проверка работы ГРП на байпасе, закрытие отключающего и байпасного кранов, сброс давления, установка защитной решётки редуктора, сигнализатор</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Станкевич Ю.А.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>